--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251102.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251102.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,60 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>746.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3639225768</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Compound - Raspberry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>57.49</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>57.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>104991837</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bob's Red Mill - Baking Flour (GF)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>62.49</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>62.49</t>
         </is>
       </c>
     </row>
